--- a/request_forms/016_request_for_additional_information_form--request_forms.xlsx
+++ b/request_forms/016_request_for_additional_information_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>request_form_additional_details</t>
+          <t>request_form_additional_details_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>request_form_comments</t>
+          <t>request_form_comments_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Request Form Comments 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>request_form_additional_details</t>
+          <t>request_form_additional_details_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Details</t>
+          <t>Request Form Additional Details 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>request_form_service_name</t>
+          <t>request_form_service_name_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Service Name</t>
+          <t>Request Form Service Name 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>request_form_service_type</t>
+          <t>request_form_service_type_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Service Type</t>
+          <t>Request Form Service Type 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>request_form_service_date</t>
+          <t>request_form_service_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Service Date</t>
+          <t>Request Form Service Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>request_form_service_time</t>
+          <t>request_form_service_time_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Service Time</t>
+          <t>Request Form Service Time 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>request_form_attachment</t>
+          <t>request_form_attachment_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Attachment</t>
+          <t>Request Form Attachment 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>request_form_comments</t>
+          <t>request_form_comments_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Request Form Comments 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>request_form_email</t>
+          <t>request_form_email_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Request Form Email 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
